--- a/output/pdf_financials_xlsx/IVX.xlsx
+++ b/output/pdf_financials_xlsx/IVX.xlsx
@@ -2158,7 +2158,7 @@
         <v>0.595</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>-0.011</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.229</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.27</v>
@@ -2278,7 +2278,7 @@
         <v>-0.2227622519238558</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-2.81180960032135</v>
+        <v>4.599317131954208</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-5.779109589041096</v>
@@ -7463,10 +7463,10 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.595</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">

--- a/output/pdf_financials_xlsx/IVX.xlsx
+++ b/output/pdf_financials_xlsx/IVX.xlsx
@@ -20758,7 +20758,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
